--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136453598</v>
       </c>
       <c r="B9" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136453638</v>
       </c>
       <c r="B10" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136453639</v>
       </c>
       <c r="B11" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136320473</v>
       </c>
       <c r="B12" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136320487</v>
       </c>
       <c r="B13" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136320479</v>
       </c>
       <c r="B14" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136453644</v>
       </c>
       <c r="B15" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>136453645</v>
       </c>
       <c r="B16" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136453651</v>
       </c>
       <c r="B17" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136320474</v>
       </c>
       <c r="B18" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136320475</v>
       </c>
       <c r="B19" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136453604</v>
       </c>
       <c r="B20" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136453632</v>
       </c>
       <c r="B21" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136453633</v>
       </c>
       <c r="B22" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136453634</v>
       </c>
       <c r="B23" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136453630</v>
       </c>
       <c r="B24" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136453620</v>
       </c>
       <c r="B29" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136453623</v>
       </c>
       <c r="B30" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136453624</v>
       </c>
       <c r="B31" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136320490</v>
       </c>
       <c r="B32" t="n">
-        <v>93431</v>
+        <v>93434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136320473</v>
       </c>
       <c r="B12" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136320487</v>
       </c>
       <c r="B13" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136320479</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136453644</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>136453645</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136453651</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136320474</v>
       </c>
       <c r="B18" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136320475</v>
       </c>
       <c r="B19" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136453604</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136453630</v>
       </c>
       <c r="B24" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136453620</v>
       </c>
       <c r="B29" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136453623</v>
       </c>
       <c r="B30" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136453624</v>
       </c>
       <c r="B31" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136320490</v>
       </c>
       <c r="B32" t="n">
-        <v>93434</v>
+        <v>93435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136453598</v>
       </c>
       <c r="B9" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136453638</v>
       </c>
       <c r="B10" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136453639</v>
       </c>
       <c r="B11" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136320473</v>
       </c>
       <c r="B12" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136320487</v>
       </c>
       <c r="B13" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>136320479</v>
       </c>
       <c r="B14" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136453644</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>136453645</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>136453651</v>
       </c>
       <c r="B17" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>136320474</v>
       </c>
       <c r="B18" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136320475</v>
       </c>
       <c r="B19" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136453604</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136453632</v>
       </c>
       <c r="B21" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136453633</v>
       </c>
       <c r="B22" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>136453634</v>
       </c>
       <c r="B23" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136453630</v>
       </c>
       <c r="B24" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>136320491</v>
       </c>
       <c r="B25" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>136320494</v>
       </c>
       <c r="B26" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>136453565</v>
       </c>
       <c r="B27" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>136453569</v>
       </c>
       <c r="B28" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>136453620</v>
       </c>
       <c r="B29" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>136453623</v>
       </c>
       <c r="B30" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>136453624</v>
       </c>
       <c r="B31" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>136320490</v>
       </c>
       <c r="B32" t="n">
-        <v>93435</v>
+        <v>93440</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136453553</v>
+        <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>92033</v>
+        <v>93434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,34 +1347,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688682</v>
+        <v>688667</v>
       </c>
       <c r="R8" t="n">
-        <v>7412631</v>
+        <v>7412594</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,9 +1404,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,27 +1431,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453553</t>
+          <t>https://artportalen.se/Sighting/136814441</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136453598</v>
+        <v>136453553</v>
       </c>
       <c r="B9" t="n">
-        <v>87501</v>
+        <v>92033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3690</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>688374</v>
+        <v>688682</v>
       </c>
       <c r="R9" t="n">
-        <v>7412855</v>
+        <v>7412631</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1534,13 +1544,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453598</t>
+          <t>https://artportalen.se/Sighting/136453553</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136453638</v>
+        <v>136453598</v>
       </c>
       <c r="B10" t="n">
         <v>87501</v>
@@ -1575,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>688627</v>
+        <v>688374</v>
       </c>
       <c r="R10" t="n">
-        <v>7412451</v>
+        <v>7412855</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1636,13 +1646,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453638</t>
+          <t>https://artportalen.se/Sighting/136453598</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136453639</v>
+        <v>136453638</v>
       </c>
       <c r="B11" t="n">
         <v>87501</v>
@@ -1677,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>688586</v>
+        <v>688627</v>
       </c>
       <c r="R11" t="n">
-        <v>7412433</v>
+        <v>7412451</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1738,16 +1748,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453639</t>
+          <t>https://artportalen.se/Sighting/136453638</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136320473</v>
+        <v>136453639</v>
       </c>
       <c r="B12" t="n">
-        <v>93403</v>
+        <v>87501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,21 +1765,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>688625</v>
+        <v>688586</v>
       </c>
       <c r="R12" t="n">
-        <v>7412539</v>
+        <v>7412433</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1812,19 +1822,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1839,7 +1839,7 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1850,13 +1850,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320473</t>
+          <t>https://artportalen.se/Sighting/136453639</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136320487</v>
+        <v>136320473</v>
       </c>
       <c r="B13" t="n">
         <v>93403</v>
@@ -1884,35 +1884,20 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>688612</v>
+        <v>688625</v>
       </c>
       <c r="R13" t="n">
-        <v>7412681</v>
+        <v>7412539</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1941,7 +1926,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1951,7 +1936,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,7 +1945,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1978,16 +1962,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320487</t>
+          <t>https://artportalen.se/Sighting/136320473</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136320479</v>
+        <v>136320487</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,37 +1979,52 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>688599</v>
+        <v>688612</v>
       </c>
       <c r="R14" t="n">
-        <v>7412694</v>
+        <v>7412681</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2064,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,6 +2072,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,16 +2090,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320479</t>
+          <t>https://artportalen.se/Sighting/136320487</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136453644</v>
+        <v>136814488</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,37 +2107,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>688371</v>
+        <v>688612</v>
       </c>
       <c r="R15" t="n">
-        <v>7412621</v>
+        <v>7412693</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2164,9 +2164,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,24 +2191,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453644</t>
+          <t>https://artportalen.se/Sighting/136814488</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136453645</v>
+        <v>136320479</v>
       </c>
       <c r="B16" t="n">
         <v>93409</v>
@@ -2233,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>688395</v>
+        <v>688599</v>
       </c>
       <c r="R16" t="n">
-        <v>7412641</v>
+        <v>7412694</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2266,9 +2276,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2283,7 +2303,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2294,13 +2314,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453645</t>
+          <t>https://artportalen.se/Sighting/136320479</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136453651</v>
+        <v>136453644</v>
       </c>
       <c r="B17" t="n">
         <v>93409</v>
@@ -2335,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>688743</v>
+        <v>688371</v>
       </c>
       <c r="R17" t="n">
-        <v>7412560</v>
+        <v>7412621</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,38 +2416,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453651</t>
+          <t>https://artportalen.se/Sighting/136453644</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136320474</v>
+        <v>136453645</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>688598</v>
+        <v>688395</v>
       </c>
       <c r="R18" t="n">
-        <v>7412630</v>
+        <v>7412641</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2470,19 +2490,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2507,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2508,38 +2518,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320474</t>
+          <t>https://artportalen.se/Sighting/136453645</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136320475</v>
+        <v>136453651</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,13 +2559,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>688611</v>
+        <v>688743</v>
       </c>
       <c r="R19" t="n">
-        <v>7412650</v>
+        <v>7412560</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2582,19 +2592,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,7 +2609,7 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2620,16 +2620,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320475</t>
+          <t>https://artportalen.se/Sighting/136453651</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136453604</v>
+        <v>136814480</v>
       </c>
       <c r="B20" t="n">
-        <v>93421</v>
+        <v>93409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,34 +2637,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>688416</v>
+        <v>688585</v>
       </c>
       <c r="R20" t="n">
-        <v>7412828</v>
+        <v>7412719</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,9 +2694,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,27 +2721,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453604</t>
+          <t>https://artportalen.se/Sighting/136814480</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136453632</v>
+        <v>136814486</v>
       </c>
       <c r="B21" t="n">
-        <v>90705</v>
+        <v>93409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,37 +2749,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>688397</v>
+        <v>688599</v>
       </c>
       <c r="R21" t="n">
-        <v>7412673</v>
+        <v>7412701</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,9 +2806,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,49 +2833,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453632</t>
+          <t>https://artportalen.se/Sighting/136814486</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136453633</v>
+        <v>136320474</v>
       </c>
       <c r="B22" t="n">
-        <v>90705</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>688430</v>
+        <v>688598</v>
       </c>
       <c r="R22" t="n">
-        <v>7412788</v>
+        <v>7412630</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2898,9 +2918,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2915,7 +2945,7 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2926,38 +2956,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453633</t>
+          <t>https://artportalen.se/Sighting/136320474</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136453634</v>
+        <v>136320475</v>
       </c>
       <c r="B23" t="n">
-        <v>90705</v>
+        <v>93413</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,13 +2997,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>688382</v>
+        <v>688611</v>
       </c>
       <c r="R23" t="n">
-        <v>7412847</v>
+        <v>7412650</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,9 +3030,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,7 +3057,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3028,51 +3068,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453634</t>
+          <t>https://artportalen.se/Sighting/136320475</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136453630</v>
+        <v>136814481</v>
       </c>
       <c r="B24" t="n">
-        <v>93435</v>
+        <v>93413</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>688639</v>
+        <v>688584</v>
       </c>
       <c r="R24" t="n">
-        <v>7412502</v>
+        <v>7412718</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3102,45 +3142,54 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453630</t>
+          <t>https://artportalen.se/Sighting/136814481</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136320491</v>
+        <v>136453604</v>
       </c>
       <c r="B25" t="n">
-        <v>80095</v>
+        <v>93421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3148,21 +3197,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3172,10 +3221,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>688424</v>
+        <v>688416</v>
       </c>
       <c r="R25" t="n">
-        <v>7412719</v>
+        <v>7412828</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3205,19 +3254,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,7 +3271,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3243,16 +3282,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320491</t>
+          <t>https://artportalen.se/Sighting/136453604</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136320494</v>
+        <v>136453632</v>
       </c>
       <c r="B26" t="n">
-        <v>80095</v>
+        <v>90705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3260,40 +3299,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688487</v>
+        <v>688397</v>
       </c>
       <c r="R26" t="n">
-        <v>7412652</v>
+        <v>7412673</v>
       </c>
       <c r="S26" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3320,35 +3356,24 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3359,55 +3384,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320494</t>
+          <t>https://artportalen.se/Sighting/136453632</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136453565</v>
+        <v>136453633</v>
       </c>
       <c r="B27" t="n">
-        <v>57195</v>
+        <v>90705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>4962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688428</v>
+        <v>688430</v>
       </c>
       <c r="R27" t="n">
-        <v>7412790</v>
+        <v>7412788</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3442,11 +3463,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>spillning</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3470,16 +3486,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453565</t>
+          <t>https://artportalen.se/Sighting/136453633</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136453569</v>
+        <v>136453634</v>
       </c>
       <c r="B28" t="n">
-        <v>58169</v>
+        <v>90705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,21 +3503,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>4962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3511,10 +3527,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688576</v>
+        <v>688382</v>
       </c>
       <c r="R28" t="n">
-        <v>7412433</v>
+        <v>7412847</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3572,38 +3588,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453569</t>
+          <t>https://artportalen.se/Sighting/136453634</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136453620</v>
+        <v>136453630</v>
       </c>
       <c r="B29" t="n">
-        <v>98219</v>
+        <v>93435</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>5448</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3613,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688698</v>
+        <v>688639</v>
       </c>
       <c r="R29" t="n">
-        <v>7412629</v>
+        <v>7412502</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3657,6 +3673,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3674,38 +3691,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453620</t>
+          <t>https://artportalen.se/Sighting/136453630</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136453623</v>
+        <v>136320491</v>
       </c>
       <c r="B30" t="n">
-        <v>98219</v>
+        <v>80095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3732,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688725</v>
+        <v>688424</v>
       </c>
       <c r="R30" t="n">
-        <v>7412597</v>
+        <v>7412719</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3748,9 +3765,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,7 +3792,7 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -3776,54 +3803,57 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453623</t>
+          <t>https://artportalen.se/Sighting/136320491</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136453624</v>
+        <v>136320494</v>
       </c>
       <c r="B31" t="n">
-        <v>98219</v>
+        <v>80095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688670</v>
+        <v>688487</v>
       </c>
       <c r="R31" t="n">
-        <v>7412524</v>
+        <v>7412652</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3850,24 +3880,35 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -3878,51 +3919,55 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453624</t>
+          <t>https://artportalen.se/Sighting/136320494</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136320490</v>
+        <v>136453565</v>
       </c>
       <c r="B32" t="n">
-        <v>93440</v>
+        <v>57195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>232140</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688440</v>
+        <v>688428</v>
       </c>
       <c r="R32" t="n">
-        <v>7412736</v>
+        <v>7412790</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3952,19 +3997,14 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:30</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3979,7 +4019,7 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -3990,7 +4030,976 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136453565</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136453569</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>688576</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7412433</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453569</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136814439</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>688612</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7412466</v>
+      </c>
+      <c r="S34" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814439</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136453620</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>688698</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7412629</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453620</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136453623</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>688725</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7412597</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453623</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136453624</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>688670</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7412524</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453624</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136814487</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>688615</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7412698</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814487</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136320490</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>688440</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7412736</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136320490</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136814482</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7412723</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814482</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136814479</v>
+      </c>
+      <c r="B41" t="n">
+        <v>93430</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814479</t>
         </is>
       </c>
     </row>
@@ -4027,6 +5036,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>136453553</v>
       </c>
       <c r="B9" t="n">
-        <v>92033</v>
+        <v>92035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136453598</v>
       </c>
       <c r="B10" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136453638</v>
       </c>
       <c r="B11" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136453639</v>
       </c>
       <c r="B12" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136320473</v>
       </c>
       <c r="B13" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136320487</v>
       </c>
       <c r="B14" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136814488</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>136320479</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>136453644</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>136453645</v>
       </c>
       <c r="B18" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>136453651</v>
       </c>
       <c r="B19" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136814480</v>
       </c>
       <c r="B20" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136814486</v>
       </c>
       <c r="B21" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136320474</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136320475</v>
       </c>
       <c r="B23" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136814481</v>
       </c>
       <c r="B24" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>136453604</v>
       </c>
       <c r="B25" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136453632</v>
       </c>
       <c r="B26" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136453633</v>
       </c>
       <c r="B27" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136453634</v>
       </c>
       <c r="B28" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136453630</v>
       </c>
       <c r="B29" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3697,45 +3697,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136320491</v>
+        <v>136453559</v>
       </c>
       <c r="B30" t="n">
-        <v>80095</v>
+        <v>90895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688424</v>
+        <v>688597</v>
       </c>
       <c r="R30" t="n">
-        <v>7412719</v>
+        <v>7412455</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3765,34 +3776,25 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -3803,41 +3805,45 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320491</t>
+          <t>https://artportalen.se/Sighting/136453559</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136320494</v>
+        <v>136453563</v>
       </c>
       <c r="B31" t="n">
-        <v>80095</v>
+        <v>90895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3847,13 +3853,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688487</v>
+        <v>688592</v>
       </c>
       <c r="R31" t="n">
-        <v>7412652</v>
+        <v>7412486</v>
       </c>
       <c r="S31" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3880,19 +3886,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3908,7 +3904,7 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -3919,55 +3915,51 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320494</t>
+          <t>https://artportalen.se/Sighting/136453563</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136453565</v>
+        <v>136320491</v>
       </c>
       <c r="B32" t="n">
-        <v>57195</v>
+        <v>80095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688428</v>
+        <v>688424</v>
       </c>
       <c r="R32" t="n">
-        <v>7412790</v>
+        <v>7412719</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3997,14 +3989,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>spillning</t>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4019,7 +4016,7 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4030,16 +4027,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453565</t>
+          <t>https://artportalen.se/Sighting/136320491</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136453569</v>
+        <v>136320494</v>
       </c>
       <c r="B33" t="n">
-        <v>58169</v>
+        <v>80095</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4047,37 +4044,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688576</v>
+        <v>688487</v>
       </c>
       <c r="R33" t="n">
-        <v>7412433</v>
+        <v>7412652</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4104,24 +4104,35 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -4132,54 +4143,58 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453569</t>
+          <t>https://artportalen.se/Sighting/136320494</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136814439</v>
+        <v>136453565</v>
       </c>
       <c r="B34" t="n">
-        <v>58169</v>
+        <v>57195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688612</v>
+        <v>688428</v>
       </c>
       <c r="R34" t="n">
-        <v>7412466</v>
+        <v>7412790</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4206,19 +4221,14 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:01</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4233,49 +4243,49 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814439</t>
+          <t>https://artportalen.se/Sighting/136453565</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136453620</v>
+        <v>136453569</v>
       </c>
       <c r="B35" t="n">
-        <v>98219</v>
+        <v>58169</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4285,10 +4295,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688698</v>
+        <v>688576</v>
       </c>
       <c r="R35" t="n">
-        <v>7412629</v>
+        <v>7412433</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4346,54 +4356,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453620</t>
+          <t>https://artportalen.se/Sighting/136453569</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136453623</v>
+        <v>136814439</v>
       </c>
       <c r="B36" t="n">
-        <v>98219</v>
+        <v>58169</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>688725</v>
+        <v>688612</v>
       </c>
       <c r="R36" t="n">
-        <v>7412597</v>
+        <v>7412466</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4420,9 +4430,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4437,27 +4457,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453623</t>
+          <t>https://artportalen.se/Sighting/136814439</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136453624</v>
+        <v>136453620</v>
       </c>
       <c r="B37" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,10 +4509,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688670</v>
+        <v>688698</v>
       </c>
       <c r="R37" t="n">
-        <v>7412524</v>
+        <v>7412629</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4550,54 +4570,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453624</t>
+          <t>https://artportalen.se/Sighting/136453620</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136814487</v>
+        <v>136453623</v>
       </c>
       <c r="B38" t="n">
-        <v>80066</v>
+        <v>98221</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688615</v>
+        <v>688725</v>
       </c>
       <c r="R38" t="n">
-        <v>7412698</v>
+        <v>7412597</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4624,19 +4644,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4651,49 +4661,49 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814487</t>
+          <t>https://artportalen.se/Sighting/136453623</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136320490</v>
+        <v>136453624</v>
       </c>
       <c r="B39" t="n">
-        <v>93440</v>
+        <v>98221</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>232140</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4703,10 +4713,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688440</v>
+        <v>688670</v>
       </c>
       <c r="R39" t="n">
-        <v>7412736</v>
+        <v>7412524</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4736,19 +4746,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,7 +4763,7 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -4774,38 +4774,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320490</t>
+          <t>https://artportalen.se/Sighting/136453624</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136814482</v>
+        <v>136814487</v>
       </c>
       <c r="B40" t="n">
-        <v>93440</v>
+        <v>80066</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4815,13 +4815,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>688585</v>
+        <v>688615</v>
       </c>
       <c r="R40" t="n">
-        <v>7412723</v>
+        <v>7412698</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4886,51 +4886,51 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814482</t>
+          <t>https://artportalen.se/Sighting/136814487</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136814479</v>
+        <v>136320490</v>
       </c>
       <c r="B41" t="n">
-        <v>93430</v>
+        <v>93442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6331648</v>
+        <v>232140</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>688585</v>
+        <v>688440</v>
       </c>
       <c r="R41" t="n">
-        <v>7412719</v>
+        <v>7412736</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4981,23 +4981,247 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320490</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136814482</v>
+      </c>
+      <c r="B42" t="n">
+        <v>93442</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7412723</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814482</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136814479</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93432</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136814479</t>
         </is>
@@ -5045,6 +5269,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320478</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136320492</v>
       </c>
       <c r="B5" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>136453553</v>
       </c>
       <c r="B9" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136453598</v>
       </c>
       <c r="B10" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136453638</v>
       </c>
       <c r="B11" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136453639</v>
       </c>
       <c r="B12" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136320473</v>
       </c>
       <c r="B13" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136320487</v>
       </c>
       <c r="B14" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136814488</v>
       </c>
       <c r="B15" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>136320479</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>136453644</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>136453645</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>136453651</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136814480</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136814486</v>
       </c>
       <c r="B21" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>136320474</v>
       </c>
       <c r="B22" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>136320475</v>
       </c>
       <c r="B23" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136814481</v>
       </c>
       <c r="B24" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>136453604</v>
       </c>
       <c r="B25" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136453632</v>
       </c>
       <c r="B26" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136453633</v>
       </c>
       <c r="B27" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136453634</v>
       </c>
       <c r="B28" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136453630</v>
       </c>
       <c r="B29" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136453559</v>
       </c>
       <c r="B30" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136453563</v>
       </c>
       <c r="B31" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>136320491</v>
       </c>
       <c r="B32" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>136320494</v>
       </c>
       <c r="B33" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>136453620</v>
       </c>
       <c r="B37" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>136453623</v>
       </c>
       <c r="B38" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>136453624</v>
       </c>
       <c r="B39" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>136814487</v>
       </c>
       <c r="B40" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>136320490</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136814482</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136814479</v>
       </c>
       <c r="B43" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>136453553</v>
       </c>
       <c r="B9" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136453598</v>
       </c>
       <c r="B10" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136453638</v>
       </c>
       <c r="B11" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136453639</v>
       </c>
       <c r="B12" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>136814488</v>
       </c>
       <c r="B15" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>136453644</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>136453645</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>136453651</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>136814480</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>136814486</v>
       </c>
       <c r="B21" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>136814481</v>
       </c>
       <c r="B24" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>136453604</v>
       </c>
       <c r="B25" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136453632</v>
       </c>
       <c r="B26" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>136453633</v>
       </c>
       <c r="B27" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136453634</v>
       </c>
       <c r="B28" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>136453630</v>
       </c>
       <c r="B29" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>136453559</v>
       </c>
       <c r="B30" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136453563</v>
       </c>
       <c r="B31" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>136453620</v>
       </c>
       <c r="B37" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>136453623</v>
       </c>
       <c r="B38" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>136453624</v>
       </c>
       <c r="B39" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>136814487</v>
       </c>
       <c r="B40" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136814482</v>
       </c>
       <c r="B42" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>136814479</v>
       </c>
       <c r="B43" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>136453553</v>
       </c>
       <c r="B9" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136453598</v>
       </c>
       <c r="B10" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136453638</v>
       </c>
       <c r="B11" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136453639</v>
       </c>
       <c r="B12" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136320473</v>
+        <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,34 +1867,49 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Randijaur, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>688625</v>
+        <v>688304</v>
       </c>
       <c r="R13" t="n">
-        <v>7412539</v>
+        <v>7412960</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1921,22 +1936,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,30 +1950,41 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320473</t>
+          <t>https://artportalen.se/Sighting/137102763</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136320487</v>
+        <v>136320473</v>
       </c>
       <c r="B14" t="n">
         <v>93407</v>
@@ -1996,35 +2012,20 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>688612</v>
+        <v>688625</v>
       </c>
       <c r="R14" t="n">
-        <v>7412681</v>
+        <v>7412539</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2053,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,7 +2073,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2090,16 +2090,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320487</t>
+          <t>https://artportalen.se/Sighting/136320473</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136814488</v>
+        <v>136320487</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,17 +2124,32 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>688612</v>
       </c>
       <c r="R15" t="n">
-        <v>7412693</v>
+        <v>7412681</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2166,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2176,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,33 +2200,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814488</t>
+          <t>https://artportalen.se/Sighting/136320487</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136320479</v>
+        <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2219,37 +2235,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>688599</v>
+        <v>688612</v>
       </c>
       <c r="R16" t="n">
-        <v>7412694</v>
+        <v>7412693</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2278,7 +2294,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2288,7 +2304,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,27 +2319,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320479</t>
+          <t>https://artportalen.se/Sighting/136814488</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136453644</v>
+        <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93410</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,34 +2347,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Randijaur, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>688371</v>
+        <v>688157</v>
       </c>
       <c r="R17" t="n">
-        <v>7412621</v>
+        <v>7412915</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2385,12 +2416,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,33 +2430,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453644</t>
+          <t>https://artportalen.se/Sighting/137103124</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136453645</v>
+        <v>136320479</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,10 +2489,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>688395</v>
+        <v>688599</v>
       </c>
       <c r="R18" t="n">
-        <v>7412641</v>
+        <v>7412694</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2490,9 +2522,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,7 +2549,7 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -2518,16 +2560,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453645</t>
+          <t>https://artportalen.se/Sighting/136320479</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136453651</v>
+        <v>136453644</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>688743</v>
+        <v>688371</v>
       </c>
       <c r="R19" t="n">
-        <v>7412560</v>
+        <v>7412621</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2620,16 +2662,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453651</t>
+          <t>https://artportalen.se/Sighting/136453644</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136814480</v>
+        <v>136453645</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,14 +2699,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>688585</v>
+        <v>688395</v>
       </c>
       <c r="R20" t="n">
-        <v>7412719</v>
+        <v>7412641</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,19 +2736,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2721,27 +2753,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814480</t>
+          <t>https://artportalen.se/Sighting/136453645</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136814486</v>
+        <v>136453651</v>
       </c>
       <c r="B21" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,17 +2801,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>688599</v>
+        <v>688743</v>
       </c>
       <c r="R21" t="n">
-        <v>7412701</v>
+        <v>7412560</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2806,19 +2838,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,62 +2855,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814486</t>
+          <t>https://artportalen.se/Sighting/136453651</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136320474</v>
+        <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93417</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>688598</v>
+        <v>688585</v>
       </c>
       <c r="R22" t="n">
-        <v>7412630</v>
+        <v>7412719</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2920,7 +2942,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2930,7 +2952,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,65 +2967,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320474</t>
+          <t>https://artportalen.se/Sighting/136814480</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136320475</v>
+        <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93417</v>
+        <v>93416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>688611</v>
+        <v>688599</v>
       </c>
       <c r="R23" t="n">
-        <v>7412650</v>
+        <v>7412701</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,7 +3054,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3042,7 +3064,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,27 +3079,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320475</t>
+          <t>https://artportalen.se/Sighting/136814486</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136814481</v>
+        <v>136320474</v>
       </c>
       <c r="B24" t="n">
-        <v>93419</v>
+        <v>93417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3105,14 +3127,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>688584</v>
+        <v>688598</v>
       </c>
       <c r="R24" t="n">
-        <v>7412718</v>
+        <v>7412630</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3144,7 +3166,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3154,7 +3176,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3169,49 +3191,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814481</t>
+          <t>https://artportalen.se/Sighting/136320474</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136453604</v>
+        <v>136320475</v>
       </c>
       <c r="B25" t="n">
-        <v>93427</v>
+        <v>93417</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3221,13 +3243,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>688416</v>
+        <v>688611</v>
       </c>
       <c r="R25" t="n">
-        <v>7412828</v>
+        <v>7412650</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,9 +3276,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3271,7 +3303,7 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3282,51 +3314,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453604</t>
+          <t>https://artportalen.se/Sighting/136320475</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136453632</v>
+        <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>90711</v>
+        <v>93420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688397</v>
+        <v>688584</v>
       </c>
       <c r="R26" t="n">
-        <v>7412673</v>
+        <v>7412718</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3356,9 +3388,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3373,27 +3415,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453632</t>
+          <t>https://artportalen.se/Sighting/136814481</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136453633</v>
+        <v>136453604</v>
       </c>
       <c r="B27" t="n">
-        <v>90711</v>
+        <v>93428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,21 +3443,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3425,10 +3467,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688430</v>
+        <v>688416</v>
       </c>
       <c r="R27" t="n">
-        <v>7412788</v>
+        <v>7412828</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3486,16 +3528,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453633</t>
+          <t>https://artportalen.se/Sighting/136453604</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136453634</v>
+        <v>136453632</v>
       </c>
       <c r="B28" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688382</v>
+        <v>688397</v>
       </c>
       <c r="R28" t="n">
-        <v>7412847</v>
+        <v>7412673</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3588,16 +3630,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453634</t>
+          <t>https://artportalen.se/Sighting/136453632</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136453630</v>
+        <v>136453633</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>90712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3605,21 +3647,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3629,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688639</v>
+        <v>688430</v>
       </c>
       <c r="R29" t="n">
-        <v>7412502</v>
+        <v>7412788</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3673,7 +3715,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3691,62 +3732,51 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453630</t>
+          <t>https://artportalen.se/Sighting/136453633</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136453559</v>
+        <v>136453634</v>
       </c>
       <c r="B30" t="n">
-        <v>90899</v>
+        <v>90712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6286</v>
+        <v>4962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688597</v>
+        <v>688382</v>
       </c>
       <c r="R30" t="n">
-        <v>7412455</v>
+        <v>7412847</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3787,7 +3817,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3805,58 +3834,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453559</t>
+          <t>https://artportalen.se/Sighting/136453634</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136453563</v>
+        <v>136453630</v>
       </c>
       <c r="B31" t="n">
-        <v>90899</v>
+        <v>93442</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6286</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688592</v>
+        <v>688639</v>
       </c>
       <c r="R31" t="n">
-        <v>7412486</v>
+        <v>7412502</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3915,51 +3937,62 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453563</t>
+          <t>https://artportalen.se/Sighting/136453630</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136320491</v>
+        <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>80099</v>
+        <v>90900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688424</v>
+        <v>688597</v>
       </c>
       <c r="R32" t="n">
-        <v>7412719</v>
+        <v>7412455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3989,34 +4022,25 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -4027,41 +4051,45 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320491</t>
+          <t>https://artportalen.se/Sighting/136453559</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136320494</v>
+        <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>80099</v>
+        <v>90900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4071,13 +4099,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688487</v>
+        <v>688592</v>
       </c>
       <c r="R33" t="n">
-        <v>7412652</v>
+        <v>7412486</v>
       </c>
       <c r="S33" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4104,19 +4132,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4132,7 +4150,7 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -4143,55 +4161,51 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320494</t>
+          <t>https://artportalen.se/Sighting/136453563</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136453565</v>
+        <v>136320491</v>
       </c>
       <c r="B34" t="n">
-        <v>57195</v>
+        <v>80099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688428</v>
+        <v>688424</v>
       </c>
       <c r="R34" t="n">
-        <v>7412790</v>
+        <v>7412719</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4221,14 +4235,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>spillning</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4243,7 +4262,7 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -4254,16 +4273,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453565</t>
+          <t>https://artportalen.se/Sighting/136320491</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136453569</v>
+        <v>136320494</v>
       </c>
       <c r="B35" t="n">
-        <v>58169</v>
+        <v>80099</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,37 +4290,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688576</v>
+        <v>688487</v>
       </c>
       <c r="R35" t="n">
-        <v>7412433</v>
+        <v>7412652</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,24 +4350,35 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4356,54 +4389,58 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453569</t>
+          <t>https://artportalen.se/Sighting/136320494</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136814439</v>
+        <v>136453565</v>
       </c>
       <c r="B36" t="n">
-        <v>58169</v>
+        <v>57195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>688612</v>
+        <v>688428</v>
       </c>
       <c r="R36" t="n">
-        <v>7412466</v>
+        <v>7412790</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4430,19 +4467,14 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:01</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>spillning</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4457,49 +4489,49 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814439</t>
+          <t>https://artportalen.se/Sighting/136453565</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136453620</v>
+        <v>136453569</v>
       </c>
       <c r="B37" t="n">
-        <v>98229</v>
+        <v>58169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4509,10 +4541,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688698</v>
+        <v>688576</v>
       </c>
       <c r="R37" t="n">
-        <v>7412629</v>
+        <v>7412433</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4570,54 +4602,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453620</t>
+          <t>https://artportalen.se/Sighting/136453569</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136453623</v>
+        <v>136814439</v>
       </c>
       <c r="B38" t="n">
-        <v>98229</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688725</v>
+        <v>688612</v>
       </c>
       <c r="R38" t="n">
-        <v>7412597</v>
+        <v>7412466</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4644,9 +4676,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4661,27 +4703,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453623</t>
+          <t>https://artportalen.se/Sighting/136814439</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136453624</v>
+        <v>136453620</v>
       </c>
       <c r="B39" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,10 +4755,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688670</v>
+        <v>688698</v>
       </c>
       <c r="R39" t="n">
-        <v>7412524</v>
+        <v>7412629</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4774,54 +4816,54 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453624</t>
+          <t>https://artportalen.se/Sighting/136453620</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136814487</v>
+        <v>136453623</v>
       </c>
       <c r="B40" t="n">
-        <v>80072</v>
+        <v>98230</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>688615</v>
+        <v>688725</v>
       </c>
       <c r="R40" t="n">
-        <v>7412698</v>
+        <v>7412597</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4848,19 +4890,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4875,49 +4907,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814487</t>
+          <t>https://artportalen.se/Sighting/136453623</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136320490</v>
+        <v>136453624</v>
       </c>
       <c r="B41" t="n">
-        <v>93444</v>
+        <v>98230</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>232140</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4927,10 +4959,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>688440</v>
+        <v>688670</v>
       </c>
       <c r="R41" t="n">
-        <v>7412736</v>
+        <v>7412524</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4960,19 +4992,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4987,7 +5009,7 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -4998,38 +5020,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320490</t>
+          <t>https://artportalen.se/Sighting/136453624</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136814482</v>
+        <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>93446</v>
+        <v>80073</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5039,13 +5061,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>688585</v>
+        <v>688615</v>
       </c>
       <c r="R42" t="n">
-        <v>7412723</v>
+        <v>7412698</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5074,7 +5096,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5084,7 +5106,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,51 +5132,51 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814482</t>
+          <t>https://artportalen.se/Sighting/136814487</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136814479</v>
+        <v>136320490</v>
       </c>
       <c r="B43" t="n">
-        <v>93436</v>
+        <v>93444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6331648</v>
+        <v>232140</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>688585</v>
+        <v>688440</v>
       </c>
       <c r="R43" t="n">
-        <v>7412719</v>
+        <v>7412736</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5186,7 +5208,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5196,7 +5218,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5205,23 +5227,247 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320490</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136814482</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7412723</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814482</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136814479</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93437</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136814479</t>
         </is>
@@ -5271,6 +5517,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1135,7 +1135,7 @@
         <v>136453571</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453573</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>136453553</v>
       </c>
       <c r="B9" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136453598</v>
       </c>
       <c r="B10" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>136453638</v>
       </c>
       <c r="B11" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136453639</v>
       </c>
       <c r="B12" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>136453644</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>136453645</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136453651</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>136453604</v>
       </c>
       <c r="B27" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>136453632</v>
       </c>
       <c r="B28" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>136453633</v>
       </c>
       <c r="B29" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>136453634</v>
       </c>
       <c r="B30" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>136453630</v>
       </c>
       <c r="B31" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>136453620</v>
       </c>
       <c r="B39" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>136453623</v>
       </c>
       <c r="B40" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>136453624</v>
       </c>
       <c r="B41" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136814439</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>136814439</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1894,11 +1894,7 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2374,11 +2370,7 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136814439</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136814439</v>
       </c>
       <c r="B38" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 63190-2025 artfynd.xlsx
+++ b/artfynd/A 63190-2025 artfynd.xlsx
@@ -1339,7 +1339,7 @@
         <v>136814441</v>
       </c>
       <c r="B8" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>137102763</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>136814488</v>
       </c>
       <c r="B16" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>137103124</v>
       </c>
       <c r="B17" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>136814480</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>136814486</v>
       </c>
       <c r="B23" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136814481</v>
       </c>
       <c r="B26" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>136453559</v>
       </c>
       <c r="B32" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136453563</v>
       </c>
       <c r="B33" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136814439</v>
       </c>
       <c r="B38" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>136814487</v>
       </c>
       <c r="B42" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>136814482</v>
       </c>
       <c r="B44" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>136814479</v>
       </c>
       <c r="B45" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
